--- a/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
+++ b/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
@@ -107,18 +107,18 @@
     <t xml:space="preserve">Chickenpox</t>
   </si>
   <si>
+    <t xml:space="preserve">Mumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubella</t>
+  </si>
+  <si>
     <t xml:space="preserve">Suppressed</t>
   </si>
   <si>
-    <t xml:space="preserve">Mumps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scarlet fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rubella</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dengue fever</t>
   </si>
   <si>
@@ -464,49 +464,49 @@
     <t xml:space="preserve">SensitivityStable</t>
   </si>
   <si>
-    <t xml:space="preserve">Neural Network</t>
+    <t xml:space="preserve">SARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative review needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recalibrate and monitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBATS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low priority routine review</t>
   </si>
   <si>
     <t xml:space="preserve">High priority manual review</t>
   </si>
   <si>
-    <t xml:space="preserve">Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recalibrate and monitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moderate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBATS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low priority routine review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative review needed</t>
+    <t xml:space="preserve">ARIMA + Fourier</t>
   </si>
   <si>
     <t xml:space="preserve">Hybrid</t>
   </si>
   <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
     <t xml:space="preserve">No deficit monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial</t>
   </si>
   <si>
     <t xml:space="preserve">Recovered but recalibrate seasonality</t>
@@ -926,13 +926,13 @@
         <v>44866</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="G2" t="n">
         <v>34</v>
       </c>
       <c r="H2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>44621</v>
@@ -982,33 +982,29 @@
         <v>43891</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3"/>
-      <c r="I3" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="J3" t="n">
-        <v>26</v>
-      </c>
+      <c r="I3" s="1"/>
+      <c r="J3"/>
       <c r="K3" s="1" t="n">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="L3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>45992</v>
+        <v>45901</v>
       </c>
       <c r="N3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>
@@ -1020,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="b">
         <v>1</v>
@@ -1034,42 +1030,50 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>43862</v>
+        <v>43831</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45992</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>45809</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>45839</v>
+      </c>
       <c r="F4" s="1"/>
-      <c r="G4"/>
+      <c r="G4" t="n">
+        <v>66</v>
+      </c>
       <c r="H4"/>
       <c r="I4" s="1" t="n">
-        <v>45292</v>
+        <v>44013</v>
       </c>
       <c r="J4" t="n">
-        <v>48</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4"/>
+        <v>6</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="L4" t="n">
+        <v>66</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4"/>
       <c r="O4" t="s">
         <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -1077,7 +1081,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1086,27 +1090,27 @@
         <v>43831</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45505</v>
+        <v>45870</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H5"/>
       <c r="I5" s="1" t="n">
-        <v>44774</v>
+        <v>43831</v>
       </c>
       <c r="J5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>45597</v>
+        <v>45901</v>
       </c>
       <c r="L5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5"/>
@@ -1131,7 +1135,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1189,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>43831</v>
@@ -1204,12 +1208,8 @@
       <c r="F7" s="1"/>
       <c r="G7"/>
       <c r="H7"/>
-      <c r="I7" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
+      <c r="I7" s="1"/>
+      <c r="J7"/>
       <c r="K7" s="1"/>
       <c r="L7"/>
       <c r="M7" s="1"/>
@@ -1218,13 +1218,13 @@
         <v>22</v>
       </c>
       <c r="P7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -1339,40 +1339,36 @@
         <v>21</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>43983</v>
+        <v>43952</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>44805</v>
+        <v>45352</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10"/>
       <c r="K10" s="1" t="n">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M10" s="1" t="n">
-        <v>44743</v>
+        <v>45170</v>
       </c>
       <c r="N10" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="O10" t="s">
         <v>33</v>
@@ -1384,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
@@ -1401,40 +1397,40 @@
         <v>21</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>43891</v>
+        <v>43983</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44652</v>
+        <v>44501</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>44682</v>
+        <v>44166</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>43922</v>
+        <v>43983</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>44682</v>
+        <v>44166</v>
       </c>
       <c r="L11" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>44805</v>
+        <v>44743</v>
       </c>
       <c r="N11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O11" t="s">
         <v>33</v>
@@ -1463,7 +1459,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>44652</v>
@@ -1472,19 +1468,19 @@
         <v>44682</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45078</v>
+        <v>44927</v>
       </c>
       <c r="G12" t="n">
         <v>28</v>
       </c>
       <c r="H12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>43983</v>
+        <v>43952</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>44682</v>
@@ -1493,10 +1489,10 @@
         <v>28</v>
       </c>
       <c r="M12" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="N12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O12" t="s">
         <v>33</v>
@@ -1534,20 +1530,16 @@
         <v>43983</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13"/>
       <c r="K13" s="1" t="n">
         <v>43983</v>
       </c>
@@ -1555,10 +1547,10 @@
         <v>5</v>
       </c>
       <c r="M13" s="1" t="n">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13" t="s">
         <v>33</v>
@@ -1570,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="b">
         <v>1</v>
@@ -1605,10 +1597,10 @@
         <v>32</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>44896</v>
+        <v>44866</v>
       </c>
       <c r="J14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>44105</v>
@@ -1649,40 +1641,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>44378</v>
+        <v>44287</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44682</v>
+        <v>44743</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>44713</v>
+        <v>44774</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="G15" t="n">
+        <v>31</v>
+      </c>
+      <c r="H15" t="n">
+        <v>39</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>44287</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="L15" t="n">
+        <v>31</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>44927</v>
       </c>
-      <c r="G15" t="n">
-        <v>29</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="N15" t="n">
         <v>36</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="J15" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="L15" t="n">
-        <v>29</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="N15" t="n">
-        <v>34</v>
       </c>
       <c r="O15" t="s">
         <v>42</v>
@@ -1711,10 +1703,10 @@
         <v>25</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>43891</v>
+        <v>43831</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44682</v>
+        <v>45352</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>44774</v>
@@ -1736,12 +1728,8 @@
       <c r="L16" t="n">
         <v>31</v>
       </c>
-      <c r="M16" s="1" t="n">
-        <v>45748</v>
-      </c>
-      <c r="N16" t="n">
-        <v>63</v>
-      </c>
+      <c r="M16" s="1"/>
+      <c r="N16"/>
       <c r="O16" t="s">
         <v>42</v>
       </c>
@@ -1758,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1787,10 +1775,10 @@
         <v>54</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>44682</v>
+        <v>43831</v>
       </c>
       <c r="J17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>44743</v>
@@ -1834,14 +1822,14 @@
         <v>43831</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45200</v>
+        <v>45992</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18"/>
       <c r="I18" s="1" t="n">
@@ -1851,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M18" s="1"/>
       <c r="N18"/>
@@ -1885,7 +1873,7 @@
         <v>21</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>44835</v>
@@ -1894,13 +1882,13 @@
         <v>44927</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45689</v>
+        <v>45597</v>
       </c>
       <c r="G19" t="n">
         <v>36</v>
       </c>
       <c r="H19" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I19" s="1" t="n">
         <v>44075</v>
@@ -1915,10 +1903,10 @@
         <v>36</v>
       </c>
       <c r="M19" s="1" t="n">
-        <v>45413</v>
+        <v>45383</v>
       </c>
       <c r="N19" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O19" t="s">
         <v>48</v>
@@ -1944,45 +1932,61 @@
         <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>43952</v>
+        <v>44317</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45992</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20"/>
-      <c r="H20"/>
+        <v>44896</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="G20" t="n">
+        <v>36</v>
+      </c>
+      <c r="H20" t="n">
+        <v>54</v>
+      </c>
       <c r="I20" s="1" t="n">
-        <v>43952</v>
+        <v>44562</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20"/>
-      <c r="M20" s="1"/>
-      <c r="N20"/>
+        <v>24</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="L20" t="n">
+        <v>36</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="N20" t="n">
+        <v>49</v>
+      </c>
       <c r="O20" t="s">
         <v>48</v>
       </c>
       <c r="P20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
       <c r="S20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1996,16 +2000,16 @@
         <v>43891</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44958</v>
+        <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="G21" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H21" t="n">
         <v>52</v>
@@ -2017,10 +2021,10 @@
         <v>5</v>
       </c>
       <c r="K21" s="1" t="n">
-        <v>45078</v>
+        <v>44986</v>
       </c>
       <c r="L21" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M21" s="1" t="n">
         <v>45323</v>
@@ -2058,16 +2062,16 @@
         <v>43891</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>45108</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>45139</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="G22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H22" t="n">
         <v>56</v>
@@ -2079,16 +2083,16 @@
         <v>2</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="N22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O22" t="s">
         <v>48</v>
@@ -2126,13 +2130,13 @@
         <v>44927</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="G23" t="n">
         <v>36</v>
       </c>
       <c r="H23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>44774</v>
@@ -2193,10 +2197,10 @@
       </c>
       <c r="H24"/>
       <c r="I24" s="1" t="n">
-        <v>43952</v>
+        <v>44044</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K24" s="1" t="n">
         <v>45292</v>
@@ -2205,10 +2209,10 @@
         <v>48</v>
       </c>
       <c r="M24" s="1" t="n">
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O24" t="s">
         <v>48</v>
@@ -2240,19 +2244,19 @@
         <v>43831</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44652</v>
+        <v>44562</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="G25" t="n">
         <v>28</v>
       </c>
       <c r="H25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>43831</v>
@@ -2366,14 +2370,18 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2"/>
+        <v>26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>66</v>
+      </c>
       <c r="E2"/>
       <c r="F2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G2"/>
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>66</v>
+      </c>
       <c r="H2"/>
       <c r="I2" t="s">
         <v>147</v>
@@ -2382,13 +2390,13 @@
         <v>-1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L2" t="n">
         <v>0.397693104035921</v>
       </c>
       <c r="M2" t="n">
-        <v>0.282</v>
+        <v>0.889</v>
       </c>
       <c r="N2" t="s">
         <v>148</v>
@@ -2417,17 +2425,15 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3"/>
-      <c r="F3" t="n">
-        <v>26</v>
-      </c>
+      <c r="F3"/>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I3" t="s">
         <v>151</v>
@@ -2436,16 +2442,16 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0.953364088531098</v>
       </c>
       <c r="M3" t="n">
-        <v>0.268</v>
+        <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -2454,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R3" t="s">
         <v>150</v>
@@ -2462,7 +2468,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -2471,45 +2477,45 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="E4"/>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>0.740898804489451</v>
       </c>
       <c r="M4" t="n">
-        <v>0.829</v>
+        <v>0.402</v>
       </c>
       <c r="N4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="s">
         <v>154</v>
       </c>
       <c r="R4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -2526,7 +2532,7 @@
         <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
         <v>26</v>
@@ -2538,7 +2544,7 @@
         <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -2550,10 +2556,10 @@
         <v>0.97291273118912</v>
       </c>
       <c r="M5" t="n">
-        <v>0.785</v>
+        <v>0.835</v>
       </c>
       <c r="N5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -2562,7 +2568,7 @@
         <v>3</v>
       </c>
       <c r="Q5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="R5" t="s">
         <v>150</v>
@@ -2570,23 +2576,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
+      <c r="F6"/>
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -2598,10 +2602,10 @@
         <v>2.01706188548294</v>
       </c>
       <c r="M6" t="n">
-        <v>0.708</v>
+        <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -2610,7 +2614,7 @@
         <v>3</v>
       </c>
       <c r="Q6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R6" t="s">
         <v>150</v>
@@ -2618,7 +2622,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -2640,7 +2644,7 @@
         <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J7" t="n">
         <v>-1</v>
@@ -2652,10 +2656,10 @@
         <v>3.96767140575221</v>
       </c>
       <c r="M7" t="n">
-        <v>0.476</v>
+        <v>0.48</v>
       </c>
       <c r="N7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -2664,7 +2668,7 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="R7" t="s">
         <v>150</v>
@@ -2694,7 +2698,7 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2709,7 +2713,7 @@
         <v>0.383</v>
       </c>
       <c r="N8" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -2718,7 +2722,7 @@
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="R8" t="s">
         <v>150</v>
@@ -2735,22 +2739,22 @@
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -2762,19 +2766,19 @@
         <v>0.809430163124035</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.773</v>
       </c>
       <c r="N9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="R9" t="s">
         <v>150</v>
@@ -2796,7 +2800,7 @@
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2808,22 +2812,22 @@
         <v>1.55516542098363</v>
       </c>
       <c r="M10" t="n">
-        <v>0.469</v>
+        <v>0.523</v>
       </c>
       <c r="N10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="R10" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -2840,19 +2844,19 @@
         <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>28</v>
       </c>
       <c r="H11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J11" t="n">
         <v>-2</v>
@@ -2873,10 +2877,10 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R11" t="s">
         <v>150</v>
@@ -2896,19 +2900,17 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F12"/>
       <c r="G12" t="n">
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2920,22 +2922,22 @@
         <v>0.800286327845383</v>
       </c>
       <c r="M12" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -2949,22 +2951,20 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F13"/>
       <c r="G13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2976,19 +2976,19 @@
         <v>1.01218438136385</v>
       </c>
       <c r="M13" t="n">
-        <v>0.481</v>
+        <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="R13" t="s">
         <v>150</v>
@@ -3005,22 +3005,22 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
+        <v>39</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31</v>
+      </c>
+      <c r="H14" t="n">
         <v>36</v>
       </c>
-      <c r="F14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G14" t="n">
-        <v>29</v>
-      </c>
-      <c r="H14" t="n">
-        <v>34</v>
-      </c>
       <c r="I14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3032,10 +3032,10 @@
         <v>1.02588093806374</v>
       </c>
       <c r="M14" t="n">
-        <v>0.618</v>
+        <v>0.539</v>
       </c>
       <c r="N14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
@@ -3044,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="R14" t="s">
         <v>150</v>
@@ -3061,18 +3061,18 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15"/>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15"/>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J15" t="n">
         <v>-5</v>
@@ -3084,10 +3084,10 @@
         <v>0.377556418821893</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.961</v>
       </c>
       <c r="N15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R15" t="s">
         <v>150</v>
@@ -3119,7 +3119,7 @@
         <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
@@ -3128,13 +3128,13 @@
         <v>31</v>
       </c>
       <c r="I16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1.22543403300255</v>
@@ -3143,16 +3143,16 @@
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R16" t="s">
         <v>150</v>
@@ -3178,9 +3178,7 @@
       <c r="G17" t="n">
         <v>31</v>
       </c>
-      <c r="H17" t="n">
-        <v>63</v>
-      </c>
+      <c r="H17"/>
       <c r="I17" t="s">
         <v>163</v>
       </c>
@@ -3194,22 +3192,22 @@
         <v>1.32133518776078</v>
       </c>
       <c r="M17" t="n">
-        <v>0.297</v>
+        <v>0.375</v>
       </c>
       <c r="N17" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="O17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>3</v>
       </c>
       <c r="Q17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="R17" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18">
@@ -3229,7 +3227,7 @@
         <v>54</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
@@ -3238,13 +3236,13 @@
         <v>48</v>
       </c>
       <c r="I18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L18" t="n">
         <v>0.807165912194936</v>
@@ -3253,19 +3251,19 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R18" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
@@ -3279,7 +3277,7 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
         <v>56</v>
@@ -3288,10 +3286,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H19" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I19" t="s">
         <v>163</v>
@@ -3306,7 +3304,7 @@
         <v>0.850572796266951</v>
       </c>
       <c r="M19" t="n">
-        <v>0.666</v>
+        <v>0.846</v>
       </c>
       <c r="N19" t="s">
         <v>162</v>
@@ -3339,16 +3337,16 @@
       </c>
       <c r="E20"/>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>48</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -3360,22 +3358,22 @@
         <v>1.06488533616557</v>
       </c>
       <c r="M20" t="n">
-        <v>0.984</v>
+        <v>0.772</v>
       </c>
       <c r="N20" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="R20" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
@@ -3392,7 +3390,7 @@
         <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F21" t="n">
         <v>31</v>
@@ -3404,13 +3402,13 @@
         <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>1.06593080934718</v>
@@ -3428,7 +3426,7 @@
         <v>2</v>
       </c>
       <c r="Q21" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R21" t="s">
         <v>150</v>
@@ -3448,7 +3446,7 @@
         <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
@@ -3457,10 +3455,10 @@
         <v>36</v>
       </c>
       <c r="H22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3472,22 +3470,22 @@
         <v>1.06171933784801</v>
       </c>
       <c r="M22" t="n">
-        <v>0.69</v>
+        <v>0.822</v>
       </c>
       <c r="N22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="s">
         <v>149</v>
       </c>
       <c r="R22" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23">
@@ -3501,7 +3499,7 @@
         <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
         <v>52</v>
@@ -3510,13 +3508,13 @@
         <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H23" t="n">
         <v>49</v>
       </c>
       <c r="I23" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="J23" t="n">
         <v>2</v>
@@ -3537,13 +3535,13 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="R23" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
@@ -3560,7 +3558,7 @@
         <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3572,7 +3570,7 @@
         <v>31</v>
       </c>
       <c r="I24" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
@@ -3584,7 +3582,7 @@
         <v>0.869950370253663</v>
       </c>
       <c r="M24" t="n">
-        <v>0.864</v>
+        <v>0.947</v>
       </c>
       <c r="N24" t="s">
         <v>162</v>
@@ -3596,7 +3594,7 @@
         <v>3</v>
       </c>
       <c r="Q24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R24" t="s">
         <v>150</v>
@@ -3610,41 +3608,49 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25"/>
-      <c r="E25"/>
+        <v>23</v>
+      </c>
+      <c r="D25" t="n">
+        <v>36</v>
+      </c>
+      <c r="E25" t="n">
+        <v>54</v>
+      </c>
       <c r="F25" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25"/>
-      <c r="H25"/>
+        <v>24</v>
+      </c>
+      <c r="G25" t="n">
+        <v>36</v>
+      </c>
+      <c r="H25" t="n">
+        <v>49</v>
+      </c>
       <c r="I25" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="J25" t="n">
         <v>-2</v>
       </c>
       <c r="K25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>1.02186511965192</v>
       </c>
       <c r="M25" t="n">
-        <v>0.395</v>
+        <v>0.616</v>
       </c>
       <c r="N25" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="R25" t="s">
         <v>150</v>
@@ -3682,7 +3688,7 @@
         <v>16</v>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -3690,7 +3696,7 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -3698,7 +3704,7 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -3779,19 +3785,17 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="E2"/>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -3802,7 +3806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -3811,13 +3815,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G3"/>
       <c r="H3" t="b">
@@ -3832,7 +3836,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -3841,17 +3845,15 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
-      </c>
-      <c r="G4" t="n">
         <v>68</v>
       </c>
+      <c r="G4"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
@@ -3859,30 +3861,30 @@
         <v>1</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -3896,25 +3898,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -3928,7 +3930,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
         <v>42</v>
@@ -3937,13 +3939,13 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G7"/>
       <c r="H7" t="b">
@@ -3958,33 +3960,63 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="n">
+        <v>47</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>47</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
         <v>48</v>
       </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="n">
         <v>48</v>
       </c>
-      <c r="G8" t="n">
-        <v>63</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G9" t="n">
+        <v>66</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4033,10 +4065,10 @@
         <v>70</v>
       </c>
       <c r="B2" t="n">
-        <v>0.398571680624258</v>
+        <v>0.412452904222956</v>
       </c>
       <c r="C2" t="n">
-        <v>0.340025887987675</v>
+        <v>0.36736688790585</v>
       </c>
       <c r="D2" t="n">
         <v>50.8385958141321</v>
@@ -4062,10 +4094,10 @@
         <v>71</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4933490417478</v>
+        <v>0.530554511020857</v>
       </c>
       <c r="C3" t="n">
-        <v>0.458016417449709</v>
+        <v>0.535319039847719</v>
       </c>
       <c r="D3" t="n">
         <v>27.128349718382</v>
@@ -4091,10 +4123,10 @@
         <v>72</v>
       </c>
       <c r="B4" t="n">
-        <v>1.00118564292273</v>
+        <v>1.18493304889419</v>
       </c>
       <c r="C4" t="n">
-        <v>0.904456932616067</v>
+        <v>1.09275750382189</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4110,10 +4142,10 @@
         <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>1.62893843719269</v>
+        <v>1.87249914641208</v>
       </c>
       <c r="C5" t="n">
-        <v>1.43161993988489</v>
+        <v>1.82955861084893</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -4146,7 +4178,7 @@
         <v>76</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.59</v>
+        <v>-0.678</v>
       </c>
     </row>
     <row r="3">
@@ -4154,7 +4186,7 @@
         <v>77</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.703</v>
+        <v>-0.778</v>
       </c>
     </row>
     <row r="4">
@@ -4162,7 +4194,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.628</v>
+        <v>-0.582</v>
       </c>
     </row>
     <row r="5">
@@ -4170,7 +4202,7 @@
         <v>79</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.628</v>
+        <v>-0.739</v>
       </c>
     </row>
     <row r="6">
@@ -4178,7 +4210,7 @@
         <v>80</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.493</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="7">
@@ -4186,7 +4218,7 @@
         <v>81</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.268</v>
+        <v>-0.136</v>
       </c>
     </row>
     <row r="8">
@@ -4194,7 +4226,7 @@
         <v>82</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.534</v>
+        <v>-0.424</v>
       </c>
     </row>
   </sheetData>
@@ -4242,7 +4274,7 @@
         <v>43922</v>
       </c>
       <c r="C2" t="n">
-        <v>0.386296226252637</v>
+        <v>0.443272511253297</v>
       </c>
       <c r="D2" t="n">
         <v>76.264</v>
@@ -4268,7 +4300,7 @@
         <v>44409</v>
       </c>
       <c r="C3" t="n">
-        <v>0.262089616906255</v>
+        <v>0.220670442551</v>
       </c>
       <c r="D3" t="n">
         <v>73.2232258064516</v>
@@ -4294,7 +4326,7 @@
         <v>44835</v>
       </c>
       <c r="C4" t="n">
-        <v>0.671448900238039</v>
+        <v>0.649851716189404</v>
       </c>
       <c r="D4" t="n">
         <v>5.56</v>
@@ -4320,7 +4352,7 @@
         <v>45108</v>
       </c>
       <c r="C5" t="n">
-        <v>0.954080167660761</v>
+        <v>1.05836150742464</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>

--- a/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
+++ b/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
@@ -1100,12 +1100,8 @@
         <v>68</v>
       </c>
       <c r="H5"/>
-      <c r="I5" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
+      <c r="I5" s="1"/>
+      <c r="J5"/>
       <c r="K5" s="1" t="n">
         <v>45901</v>
       </c>
@@ -1124,7 +1120,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -1706,7 +1702,7 @@
         <v>43831</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45352</v>
+        <v>45809</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>44774</v>
@@ -2480,21 +2476,19 @@
         <v>68</v>
       </c>
       <c r="E4"/>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F4"/>
       <c r="G4" t="n">
         <v>68</v>
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>0.740898804489451</v>
@@ -3696,7 +3690,7 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -3720,7 +3714,7 @@
         <v>58</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -3847,15 +3841,13 @@
       <c r="D4" t="n">
         <v>68</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4"/>
       <c r="F4" t="n">
         <v>68</v>
       </c>
       <c r="G4"/>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -4065,10 +4057,10 @@
         <v>70</v>
       </c>
       <c r="B2" t="n">
-        <v>0.412452904222956</v>
+        <v>0.412447463457986</v>
       </c>
       <c r="C2" t="n">
-        <v>0.36736688790585</v>
+        <v>0.367389320361059</v>
       </c>
       <c r="D2" t="n">
         <v>50.8385958141321</v>
@@ -4094,10 +4086,10 @@
         <v>71</v>
       </c>
       <c r="B3" t="n">
-        <v>0.530554511020857</v>
+        <v>0.530553469150705</v>
       </c>
       <c r="C3" t="n">
-        <v>0.535319039847719</v>
+        <v>0.535376328879821</v>
       </c>
       <c r="D3" t="n">
         <v>27.128349718382</v>
@@ -4123,10 +4115,10 @@
         <v>72</v>
       </c>
       <c r="B4" t="n">
-        <v>1.18493304889419</v>
+        <v>1.18483475141354</v>
       </c>
       <c r="C4" t="n">
-        <v>1.09275750382189</v>
+        <v>1.09292213114382</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4142,10 +4134,10 @@
         <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>1.87249914641208</v>
+        <v>1.87239240743156</v>
       </c>
       <c r="C5" t="n">
-        <v>1.82955861084893</v>
+        <v>1.83004068643568</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -4274,7 +4266,7 @@
         <v>43922</v>
       </c>
       <c r="C2" t="n">
-        <v>0.443272511253297</v>
+        <v>0.443242653089125</v>
       </c>
       <c r="D2" t="n">
         <v>76.264</v>
@@ -4300,7 +4292,7 @@
         <v>44409</v>
       </c>
       <c r="C3" t="n">
-        <v>0.220670442551</v>
+        <v>0.220707013046248</v>
       </c>
       <c r="D3" t="n">
         <v>73.2232258064516</v>
@@ -4326,7 +4318,7 @@
         <v>44835</v>
       </c>
       <c r="C4" t="n">
-        <v>0.649851716189404</v>
+        <v>0.649815907519308</v>
       </c>
       <c r="D4" t="n">
         <v>5.56</v>
@@ -4352,7 +4344,7 @@
         <v>45108</v>
       </c>
       <c r="C5" t="n">
-        <v>1.05836150742464</v>
+        <v>1.05862714472311</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>

--- a/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
+++ b/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
@@ -485,19 +485,19 @@
     <t xml:space="preserve">Recalibrate and monitor</t>
   </si>
   <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBATS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low priority routine review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High priority manual review</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBATS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low priority routine review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High priority manual review</t>
   </si>
   <si>
     <t xml:space="preserve">ARIMA + Fourier</t>
@@ -519,7 +519,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -556,7 +558,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,13 +1586,13 @@
         <v>44105</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="G14" t="n">
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="1" t="n">
         <v>44866</v>
@@ -1637,40 +1639,40 @@
         <v>21</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>44287</v>
+        <v>44409</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44743</v>
+        <v>44682</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>45017</v>
+        <v>44896</v>
       </c>
       <c r="G15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H15" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>44287</v>
+        <v>44562</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>44774</v>
+        <v>44713</v>
       </c>
       <c r="L15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M15" s="1" t="n">
-        <v>44927</v>
+        <v>44835</v>
       </c>
       <c r="N15" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O15" t="s">
         <v>42</v>
@@ -1702,7 +1704,7 @@
         <v>43831</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45809</v>
+        <v>45139</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>44774</v>
@@ -1713,10 +1715,10 @@
       </c>
       <c r="H16"/>
       <c r="I16" s="1" t="n">
-        <v>43922</v>
+        <v>43831</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>44774</v>
@@ -1931,40 +1933,40 @@
         <v>21</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>44317</v>
+        <v>44409</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44896</v>
+        <v>44743</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45474</v>
+        <v>45047</v>
       </c>
       <c r="G20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H20" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>44562</v>
+        <v>44409</v>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>44927</v>
+        <v>44866</v>
       </c>
       <c r="L20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="M20" s="1" t="n">
-        <v>45323</v>
+        <v>44958</v>
       </c>
       <c r="N20" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="O20" t="s">
         <v>48</v>
@@ -2058,19 +2060,19 @@
         <v>43891</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45078</v>
+        <v>44958</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="G22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>43891</v>
@@ -2079,16 +2081,16 @@
         <v>2</v>
       </c>
       <c r="K22" s="1" t="n">
-        <v>45108</v>
+        <v>45047</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M22" s="1" t="n">
-        <v>45413</v>
+        <v>45383</v>
       </c>
       <c r="N22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O22" t="s">
         <v>48</v>
@@ -2453,7 +2455,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="s">
         <v>152</v>
@@ -2494,7 +2496,7 @@
         <v>0.740898804489451</v>
       </c>
       <c r="M4" t="n">
-        <v>0.402</v>
+        <v>1</v>
       </c>
       <c r="N4" t="s">
         <v>153</v>
@@ -2506,10 +2508,10 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
+        <v>152</v>
+      </c>
+      <c r="R4" t="s">
         <v>154</v>
-      </c>
-      <c r="R4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="5">
@@ -2538,7 +2540,7 @@
         <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -2553,13 +2555,13 @@
         <v>0.835</v>
       </c>
       <c r="N5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="s">
         <v>149</v>
@@ -2599,13 +2601,13 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="s">
         <v>152</v>
@@ -2638,7 +2640,7 @@
         <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J7" t="n">
         <v>-1</v>
@@ -2662,7 +2664,7 @@
         <v>3</v>
       </c>
       <c r="Q7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R7" t="s">
         <v>150</v>
@@ -2692,7 +2694,7 @@
         <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2716,7 +2718,7 @@
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R8" t="s">
         <v>150</v>
@@ -2763,7 +2765,7 @@
         <v>0.773</v>
       </c>
       <c r="N9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -2806,7 +2808,7 @@
         <v>1.55516542098363</v>
       </c>
       <c r="M10" t="n">
-        <v>0.523</v>
+        <v>0.525</v>
       </c>
       <c r="N10" t="s">
         <v>161</v>
@@ -2818,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R10" t="s">
         <v>150</v>
@@ -2919,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -2931,7 +2933,7 @@
         <v>152</v>
       </c>
       <c r="R12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -2973,19 +2975,19 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="s">
         <v>152</v>
       </c>
       <c r="R13" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -2999,22 +3001,22 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H14" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I14" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3026,22 +3028,22 @@
         <v>1.02588093806374</v>
       </c>
       <c r="M14" t="n">
-        <v>0.539</v>
+        <v>0.628</v>
       </c>
       <c r="N14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="s">
+        <v>158</v>
+      </c>
+      <c r="R14" t="s">
         <v>154</v>
-      </c>
-      <c r="R14" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -3078,7 +3080,7 @@
         <v>0.377556418821893</v>
       </c>
       <c r="M15" t="n">
-        <v>0.961</v>
+        <v>0.923</v>
       </c>
       <c r="N15" t="s">
         <v>153</v>
@@ -3110,7 +3112,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
         <v>34</v>
@@ -3137,7 +3139,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
@@ -3167,7 +3169,7 @@
       </c>
       <c r="E17"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>31</v>
@@ -3186,7 +3188,7 @@
         <v>1.32133518776078</v>
       </c>
       <c r="M17" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="N17" t="s">
         <v>148</v>
@@ -3198,7 +3200,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R17" t="s">
         <v>150</v>
@@ -3245,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
@@ -3257,7 +3259,7 @@
         <v>152</v>
       </c>
       <c r="R18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19">
@@ -3271,19 +3273,19 @@
         <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H19" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I19" t="s">
         <v>163</v>
@@ -3298,7 +3300,7 @@
         <v>0.850572796266951</v>
       </c>
       <c r="M19" t="n">
-        <v>0.846</v>
+        <v>0.773</v>
       </c>
       <c r="N19" t="s">
         <v>162</v>
@@ -3307,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="s">
         <v>149</v>
@@ -3452,7 +3454,7 @@
         <v>51</v>
       </c>
       <c r="I22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3467,7 +3469,7 @@
         <v>0.822</v>
       </c>
       <c r="N22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
@@ -3479,7 +3481,7 @@
         <v>149</v>
       </c>
       <c r="R22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -3529,7 +3531,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="s">
         <v>152</v>
@@ -3605,34 +3607,34 @@
         <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H25" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="J25" t="n">
         <v>-2</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L25" t="n">
         <v>1.02186511965192</v>
       </c>
       <c r="M25" t="n">
-        <v>0.616</v>
+        <v>0.3</v>
       </c>
       <c r="N25" t="s">
         <v>162</v>
@@ -3644,7 +3646,7 @@
         <v>3</v>
       </c>
       <c r="Q25" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="R25" t="s">
         <v>150</v>
@@ -3934,7 +3936,7 @@
         <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>31</v>
@@ -4057,10 +4059,10 @@
         <v>70</v>
       </c>
       <c r="B2" t="n">
-        <v>0.412447463457986</v>
+        <v>0.41263055425183</v>
       </c>
       <c r="C2" t="n">
-        <v>0.367389320361059</v>
+        <v>0.368424681840787</v>
       </c>
       <c r="D2" t="n">
         <v>50.8385958141321</v>
@@ -4086,10 +4088,10 @@
         <v>71</v>
       </c>
       <c r="B3" t="n">
-        <v>0.530553469150705</v>
+        <v>0.530880526542157</v>
       </c>
       <c r="C3" t="n">
-        <v>0.535376328879821</v>
+        <v>0.535758846329667</v>
       </c>
       <c r="D3" t="n">
         <v>27.128349718382</v>
@@ -4115,10 +4117,10 @@
         <v>72</v>
       </c>
       <c r="B4" t="n">
-        <v>1.18483475141354</v>
+        <v>1.18719956226668</v>
       </c>
       <c r="C4" t="n">
-        <v>1.09292213114382</v>
+        <v>1.09299279778685</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -4134,10 +4136,10 @@
         <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>1.87239240743156</v>
+        <v>1.875651737662</v>
       </c>
       <c r="C5" t="n">
-        <v>1.83004068643568</v>
+        <v>1.83228509764116</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -4170,7 +4172,7 @@
         <v>76</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.678</v>
+        <v>-0.677</v>
       </c>
     </row>
     <row r="3">
@@ -4186,7 +4188,7 @@
         <v>78</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.582</v>
+        <v>-0.577</v>
       </c>
     </row>
     <row r="5">
@@ -4194,7 +4196,7 @@
         <v>79</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.739</v>
+        <v>-0.741</v>
       </c>
     </row>
     <row r="6">
@@ -4202,7 +4204,7 @@
         <v>80</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.64</v>
+        <v>-0.638</v>
       </c>
     </row>
     <row r="7">
@@ -4210,7 +4212,7 @@
         <v>81</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.136</v>
+        <v>-0.143</v>
       </c>
     </row>
     <row r="8">
@@ -4218,7 +4220,7 @@
         <v>82</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.424</v>
+        <v>-0.422</v>
       </c>
     </row>
   </sheetData>
@@ -4266,7 +4268,7 @@
         <v>43922</v>
       </c>
       <c r="C2" t="n">
-        <v>0.443242653089125</v>
+        <v>0.443618681190042</v>
       </c>
       <c r="D2" t="n">
         <v>76.264</v>
@@ -4292,7 +4294,7 @@
         <v>44409</v>
       </c>
       <c r="C3" t="n">
-        <v>0.220707013046248</v>
+        <v>0.220250637752789</v>
       </c>
       <c r="D3" t="n">
         <v>73.2232258064516</v>
@@ -4318,7 +4320,7 @@
         <v>44835</v>
       </c>
       <c r="C4" t="n">
-        <v>0.649815907519308</v>
+        <v>0.648814992457882</v>
       </c>
       <c r="D4" t="n">
         <v>5.56</v>
@@ -4344,7 +4346,7 @@
         <v>45108</v>
       </c>
       <c r="C5" t="n">
-        <v>1.05862714472311</v>
+        <v>1.06021025389276</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>

--- a/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
+++ b/Outcome/Appendix/Tables/New_endpoint_context_usability_summaries.xlsx
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2022 transition</t>
   </si>
   <si>
-    <t xml:space="preserve">2023-2024 WHO-context only</t>
+    <t xml:space="preserve">2023 to 2024-06 WHO-context only</t>
   </si>
   <si>
     <t xml:space="preserve">Late follow-up without external context</t>
